--- a/output/roomself_excel/2569.xlsx
+++ b/output/roomself_excel/2569.xlsx
@@ -564,10 +564,10 @@
         <v>3004</v>
       </c>
       <c r="E6" t="n">
-        <v>559</v>
+        <v>446</v>
       </c>
       <c r="F6" t="n">
-        <v>446</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7">
@@ -586,10 +586,10 @@
         <v>2420</v>
       </c>
       <c r="E7" t="n">
-        <v>508</v>
+        <v>354</v>
       </c>
       <c r="F7" t="n">
-        <v>229</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -608,10 +608,10 @@
         <v>2420</v>
       </c>
       <c r="E8" t="n">
-        <v>506</v>
+        <v>354</v>
       </c>
       <c r="F8" t="n">
-        <v>230</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
@@ -652,7 +652,7 @@
         <v>6848</v>
       </c>
       <c r="E10" t="n">
-        <v>968</v>
+        <v>789</v>
       </c>
       <c r="F10" t="n">
         <v>609</v>
@@ -674,10 +674,10 @@
         <v>6828</v>
       </c>
       <c r="E11" t="n">
-        <v>965</v>
+        <v>788</v>
       </c>
       <c r="F11" t="n">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
@@ -784,10 +784,10 @@
         <v>4192</v>
       </c>
       <c r="E16" t="n">
-        <v>490</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>456</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -806,10 +806,10 @@
         <v>4072</v>
       </c>
       <c r="E17" t="n">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>278</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -872,10 +872,10 @@
         <v>1332</v>
       </c>
       <c r="E20" t="n">
-        <v>214</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
@@ -894,10 +894,10 @@
         <v>1308</v>
       </c>
       <c r="E21" t="n">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/2569.xlsx
+++ b/output/roomself_excel/2569.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
         </is>
       </c>
     </row>
@@ -475,12 +555,40 @@
       <c r="D2" t="n">
         <v>8156</v>
       </c>
-      <c r="E2" t="n">
-        <v>965</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>719</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="G2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1282</v>
+      </c>
+      <c r="J2" t="n">
+        <v>52</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +605,48 @@
       <c r="D3" t="n">
         <v>10304</v>
       </c>
-      <c r="E3" t="n">
-        <v>965</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>719</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="G3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>124</v>
+      </c>
+      <c r="J3" t="n">
+        <v>56</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="M3" t="n">
+        <v>53</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +663,71 @@
       <c r="D4" t="n">
         <v>6636</v>
       </c>
-      <c r="E4" t="n">
-        <v>965</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>371</v>
+        <v>510</v>
+      </c>
+      <c r="G4" t="n">
+        <v>52</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>62</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>809</v>
+      </c>
+      <c r="S4" t="n">
+        <v>52</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +745,71 @@
       <c r="D5" t="n">
         <v>6612</v>
       </c>
-      <c r="E5" t="n">
-        <v>965</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>370</v>
+        <v>505</v>
+      </c>
+      <c r="G5" t="n">
+        <v>53</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>64</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>26</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>99</v>
+      </c>
+      <c r="S5" t="n">
+        <v>55</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>707</v>
+      </c>
+      <c r="V5" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +827,40 @@
       <c r="D6" t="n">
         <v>3004</v>
       </c>
-      <c r="E6" t="n">
-        <v>446</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="G6" t="n">
+        <v>52</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>288</v>
+      </c>
+      <c r="J6" t="n">
+        <v>52</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +877,40 @@
       <c r="D7" t="n">
         <v>2420</v>
       </c>
-      <c r="E7" t="n">
-        <v>354</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>177</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="G7" t="n">
+        <v>52</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>52</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +927,40 @@
       <c r="D8" t="n">
         <v>2420</v>
       </c>
-      <c r="E8" t="n">
-        <v>354</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>179</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="G8" t="n">
+        <v>53</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>126</v>
+      </c>
+      <c r="J8" t="n">
+        <v>52</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +977,40 @@
       <c r="D9" t="n">
         <v>3020</v>
       </c>
-      <c r="E9" t="n">
-        <v>448</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>342</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="G9" t="n">
+        <v>53</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>289</v>
+      </c>
+      <c r="J9" t="n">
+        <v>53</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +1027,56 @@
       <c r="D10" t="n">
         <v>6848</v>
       </c>
-      <c r="E10" t="n">
-        <v>789</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>609</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>523</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>26</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>102</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +1093,48 @@
       <c r="D11" t="n">
         <v>6828</v>
       </c>
-      <c r="E11" t="n">
-        <v>788</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>154</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G11" t="n">
+        <v>52</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>522</v>
+      </c>
+      <c r="J11" t="n">
+        <v>52</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>102</v>
+      </c>
+      <c r="M11" t="n">
+        <v>29</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1151,32 @@
       <c r="D12" t="n">
         <v>1824</v>
       </c>
-      <c r="E12" t="n">
-        <v>297</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>185</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1193,32 @@
       <c r="D13" t="n">
         <v>1828</v>
       </c>
-      <c r="E13" t="n">
-        <v>298</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>185</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1235,32 @@
       <c r="D14" t="n">
         <v>1624</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>115</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>52</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1277,32 @@
       <c r="D15" t="n">
         <v>1628</v>
       </c>
-      <c r="E15" t="n">
-        <v>358</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>116</v>
       </c>
+      <c r="G15" t="n">
+        <v>53</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1319,40 @@
       <c r="D16" t="n">
         <v>4192</v>
       </c>
-      <c r="E16" t="n">
-        <v>88</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>188</v>
+      </c>
+      <c r="J16" t="n">
+        <v>52</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1369,40 @@
       <c r="D17" t="n">
         <v>4072</v>
       </c>
-      <c r="E17" t="n">
-        <v>82</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>188</v>
+      </c>
+      <c r="J17" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1419,48 @@
       <c r="D18" t="n">
         <v>3388</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>556</v>
       </c>
-      <c r="F18" t="n">
-        <v>356</v>
-      </c>
+      <c r="G18" t="n">
+        <v>52</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>92</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>291</v>
+      </c>
+      <c r="M18" t="n">
+        <v>52</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1477,48 @@
       <c r="D19" t="n">
         <v>3392</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>280</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>557</v>
       </c>
-      <c r="F19" t="n">
-        <v>358</v>
-      </c>
+      <c r="J19" t="n">
+        <v>53</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>291</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1535,40 @@
       <c r="D20" t="n">
         <v>1332</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>68</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>60</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>188</v>
+      </c>
+      <c r="J20" t="n">
+        <v>58</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1585,40 @@
       <c r="D21" t="n">
         <v>1308</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>67</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>59</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>191</v>
+      </c>
+      <c r="J21" t="n">
+        <v>58</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/2569.xlsx
+++ b/output/roomself_excel/2569.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,66 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
         </is>
       </c>
     </row>
@@ -589,6 +649,54 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>499</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>202</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>235</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -647,6 +755,54 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>502</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>233</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -729,6 +885,30 @@
       <c r="V4" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>405</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -811,6 +991,42 @@
       <c r="V5" t="n">
         <v>53</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>331</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -861,6 +1077,42 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>83</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -911,6 +1163,54 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>138</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -961,6 +1261,54 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>136</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>83</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1011,6 +1359,42 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1077,6 +1461,30 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>94</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1135,6 +1543,30 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1177,6 +1609,30 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>161</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1219,6 +1675,30 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>160</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1261,6 +1741,18 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1303,6 +1795,18 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1353,6 +1857,30 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1403,6 +1931,30 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1461,6 +2013,42 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>237</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>253</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1519,6 +2107,42 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>228</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>254</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1569,6 +2193,30 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>177</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1619,6 +2267,30 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>177</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
